--- a/tasks/finalpool/canvas-quiz-analysis-email/groundtruth_workspace/Quiz_Performance.xlsx
+++ b/tasks/finalpool/canvas-quiz-analysis-email/groundtruth_workspace/Quiz_Performance.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,37 +429,21 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Avg_Score</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Pass_Rate_Pct</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Student_Count</t>
+          <t>Question_Count</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CMA 15005</t>
+          <t>CMA 15007</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>85.62</v>
-      </c>
-      <c r="D2" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1257</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -472,70 +456,46 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>88.47</v>
-      </c>
-      <c r="D3" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1350</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CMA 15006</t>
+          <t>CMA 15005</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>86.42</v>
-      </c>
-      <c r="D4" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1183</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CMA 15007</t>
+          <t>CMA 15003</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>84.86</v>
-      </c>
-      <c r="D5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1136</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CMA 15003</t>
+          <t>CMA 15006</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>93.56999999999999</v>
-      </c>
-      <c r="D6" t="n">
-        <v>100</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1490</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
